--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/74.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/74.xlsx
@@ -426,13 +426,13 @@
         <v>-3.927970034776659</v>
       </c>
       <c r="E2">
-        <v>-11.98761172932511</v>
+        <v>-12.28259771688238</v>
       </c>
       <c r="F2">
-        <v>-4.151998744175177</v>
+        <v>-4.463300870882037</v>
       </c>
       <c r="G2">
-        <v>-8.872429585863451</v>
+        <v>-6.7636280552099</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-3.297440567051592</v>
       </c>
       <c r="E3">
-        <v>-11.70339086552179</v>
+        <v>-13.16724003549351</v>
       </c>
       <c r="F3">
-        <v>-3.272487109559428</v>
+        <v>-4.511217783296974</v>
       </c>
       <c r="G3">
-        <v>-8.520264942595883</v>
+        <v>-6.819122042238604</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-2.586690062662806</v>
       </c>
       <c r="E4">
-        <v>-13.42046963639095</v>
+        <v>-13.6586438462359</v>
       </c>
       <c r="F4">
-        <v>-3.960735337807994</v>
+        <v>-4.179536990113844</v>
       </c>
       <c r="G4">
-        <v>-7.970345534157554</v>
+        <v>-6.647058309216692</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-1.932087875495449</v>
       </c>
       <c r="E5">
-        <v>-13.93126894402029</v>
+        <v>-13.93677194902569</v>
       </c>
       <c r="F5">
-        <v>-3.790326909173691</v>
+        <v>-4.10823609428528</v>
       </c>
       <c r="G5">
-        <v>-8.578040720397221</v>
+        <v>-7.138502260303266</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-1.359104334835471</v>
       </c>
       <c r="E6">
-        <v>-14.3640958622373</v>
+        <v>-14.67532090607465</v>
       </c>
       <c r="F6">
-        <v>-3.376086878790548</v>
+        <v>-4.16482684177493</v>
       </c>
       <c r="G6">
-        <v>-9.261658970091052</v>
+        <v>-6.551653869623639</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-0.9038378039318473</v>
       </c>
       <c r="E7">
-        <v>-13.87221443219256</v>
+        <v>-15.29896711861091</v>
       </c>
       <c r="F7">
-        <v>-3.077346115379739</v>
+        <v>-4.135321223254615</v>
       </c>
       <c r="G7">
-        <v>-8.112137683645507</v>
+        <v>-6.569182408808373</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-0.5598299785670993</v>
       </c>
       <c r="E8">
-        <v>-15.52390504396362</v>
+        <v>-16.13623790885104</v>
       </c>
       <c r="F8">
-        <v>-3.632117018913013</v>
+        <v>-3.856859722231742</v>
       </c>
       <c r="G8">
-        <v>-8.063479931328635</v>
+        <v>-6.893541316808288</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-0.3162992049800315</v>
       </c>
       <c r="E9">
-        <v>-15.58025581521889</v>
+        <v>-16.61846727577688</v>
       </c>
       <c r="F9">
-        <v>-3.050548429899175</v>
+        <v>-3.898498438100861</v>
       </c>
       <c r="G9">
-        <v>-7.969405666104754</v>
+        <v>-6.49595885526142</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-0.1453977292745602</v>
       </c>
       <c r="E10">
-        <v>-18.27098852981291</v>
+        <v>-17.93543397403471</v>
       </c>
       <c r="F10">
-        <v>-2.922501053509234</v>
+        <v>-3.567333717809675</v>
       </c>
       <c r="G10">
-        <v>-7.681111583886477</v>
+        <v>-5.89097623265192</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-0.03209826200427782</v>
       </c>
       <c r="E11">
-        <v>-17.69226760417733</v>
+        <v>-18.13088825219247</v>
       </c>
       <c r="F11">
-        <v>-2.982285985704079</v>
+        <v>-3.432299890744522</v>
       </c>
       <c r="G11">
-        <v>-7.293656200608537</v>
+        <v>-5.741975817347902</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>0.02913570165965749</v>
       </c>
       <c r="E12">
-        <v>-17.51223004645733</v>
+        <v>-19.32800988446105</v>
       </c>
       <c r="F12">
-        <v>-3.029715818086171</v>
+        <v>-3.601627299918172</v>
       </c>
       <c r="G12">
-        <v>-6.91256320189914</v>
+        <v>-5.473554722957181</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>0.0337054576558599</v>
       </c>
       <c r="E13">
-        <v>-19.42006166026455</v>
+        <v>-19.71614409561158</v>
       </c>
       <c r="F13">
-        <v>-3.46096885818801</v>
+        <v>-3.269408067923222</v>
       </c>
       <c r="G13">
-        <v>-7.061717651134033</v>
+        <v>-5.07950982033127</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-0.02705403904600002</v>
       </c>
       <c r="E14">
-        <v>-20.29504360933413</v>
+        <v>-20.11283392209125</v>
       </c>
       <c r="F14">
-        <v>-3.023021781104148</v>
+        <v>-3.203739242066291</v>
       </c>
       <c r="G14">
-        <v>-5.782640775099083</v>
+        <v>-4.590467754268521</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-0.15089873508013</v>
       </c>
       <c r="E15">
-        <v>-20.45691086750799</v>
+        <v>-21.3861462161138</v>
       </c>
       <c r="F15">
-        <v>-2.466605739908915</v>
+        <v>-3.31380110540665</v>
       </c>
       <c r="G15">
-        <v>-6.221222369704795</v>
+        <v>-4.142458760944299</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-0.3192159537519746</v>
       </c>
       <c r="E16">
-        <v>-20.57421001495512</v>
+        <v>-21.7799454075114</v>
       </c>
       <c r="F16">
-        <v>-2.6089283717513</v>
+        <v>-2.959577950091137</v>
       </c>
       <c r="G16">
-        <v>-4.618460157774438</v>
+        <v>-4.295591984936049</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-0.5003983602977722</v>
       </c>
       <c r="E17">
-        <v>-23.37936370154817</v>
+        <v>-22.90265395247302</v>
       </c>
       <c r="F17">
-        <v>-2.028869896512766</v>
+        <v>-2.613504273284365</v>
       </c>
       <c r="G17">
-        <v>-4.986943260108758</v>
+        <v>-3.584534809589617</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-0.6531816341414711</v>
       </c>
       <c r="E18">
-        <v>-22.30001052960643</v>
+        <v>-23.37086623117757</v>
       </c>
       <c r="F18">
-        <v>-2.312342191955174</v>
+        <v>-2.415501269728005</v>
       </c>
       <c r="G18">
-        <v>-4.34397169295397</v>
+        <v>-3.495905252210503</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-0.7381265314651446</v>
       </c>
       <c r="E19">
-        <v>-24.12328691405146</v>
+        <v>-23.69914020750334</v>
       </c>
       <c r="F19">
-        <v>-1.682578359079058</v>
+        <v>-2.334360197521585</v>
       </c>
       <c r="G19">
-        <v>-3.32881237689007</v>
+        <v>-3.236021292632722</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-0.7277594077839176</v>
       </c>
       <c r="E20">
-        <v>-24.94290655616107</v>
+        <v>-24.86059821412562</v>
       </c>
       <c r="F20">
-        <v>-2.031403044030527</v>
+        <v>-2.053791329825989</v>
       </c>
       <c r="G20">
-        <v>-4.395387696931354</v>
+        <v>-2.881166277064013</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-0.6093314340677617</v>
       </c>
       <c r="E21">
-        <v>-24.5146190979221</v>
+        <v>-25.97311477849611</v>
       </c>
       <c r="F21">
-        <v>-1.86886741919243</v>
+        <v>-1.836415297820357</v>
       </c>
       <c r="G21">
-        <v>-4.080443133926994</v>
+        <v>-2.742700216185137</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-0.3886673242779887</v>
       </c>
       <c r="E22">
-        <v>-26.90396572630729</v>
+        <v>-26.14853811843422</v>
       </c>
       <c r="F22">
-        <v>-1.342805244737979</v>
+        <v>-1.486023341742791</v>
       </c>
       <c r="G22">
-        <v>-3.372860859631333</v>
+        <v>-2.466801949285468</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-0.08925048342766081</v>
       </c>
       <c r="E23">
-        <v>-25.15702951922393</v>
+        <v>-26.50979274589046</v>
       </c>
       <c r="F23">
-        <v>-1.397156915137863</v>
+        <v>-1.572317687562027</v>
       </c>
       <c r="G23">
-        <v>-3.404223734404377</v>
+        <v>-2.132511768860958</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>0.2547024454766188</v>
       </c>
       <c r="E24">
-        <v>-25.92473401977319</v>
+        <v>-26.60414955397924</v>
       </c>
       <c r="F24">
-        <v>-1.486700946278281</v>
+        <v>-1.359068581957142</v>
       </c>
       <c r="G24">
-        <v>-2.820479519043585</v>
+        <v>-1.459610625713647</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>0.6036008491542511</v>
       </c>
       <c r="E25">
-        <v>-27.7968687822435</v>
+        <v>-27.03269451132035</v>
       </c>
       <c r="F25">
-        <v>-0.7587656357615905</v>
+        <v>-1.437629289703841</v>
       </c>
       <c r="G25">
-        <v>-2.568542666001152</v>
+        <v>-1.552195461148297</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>0.9203023204342513</v>
       </c>
       <c r="E26">
-        <v>-25.43119130519851</v>
+        <v>-27.59621883671838</v>
       </c>
       <c r="F26">
-        <v>-1.101807487874116</v>
+        <v>-1.130564262262301</v>
       </c>
       <c r="G26">
-        <v>-2.831857143971656</v>
+        <v>-1.84878387893254</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>1.174760289206903</v>
       </c>
       <c r="E27">
-        <v>-26.04925975492552</v>
+        <v>-27.72620604476287</v>
       </c>
       <c r="F27">
-        <v>-0.6719701276636612</v>
+        <v>-0.9976104657455775</v>
       </c>
       <c r="G27">
-        <v>-2.351438367293354</v>
+        <v>-1.70660272850051</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>1.346091813087189</v>
       </c>
       <c r="E28">
-        <v>-26.1655122931188</v>
+        <v>-27.36502617511048</v>
       </c>
       <c r="F28">
-        <v>-0.008518249250495068</v>
+        <v>-0.9482000069033927</v>
       </c>
       <c r="G28">
-        <v>-2.467929790948829</v>
+        <v>-1.280087995394924</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>1.425061792016658</v>
       </c>
       <c r="E29">
-        <v>-25.50324536847296</v>
+        <v>-27.55937985226715</v>
       </c>
       <c r="F29">
-        <v>-0.8153903463147563</v>
+        <v>-1.141208783388275</v>
       </c>
       <c r="G29">
-        <v>-2.916202469476753</v>
+        <v>-2.040955566795207</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>1.413134602762648</v>
       </c>
       <c r="E30">
-        <v>-27.3934839791082</v>
+        <v>-27.27455261961041</v>
       </c>
       <c r="F30">
-        <v>-1.334722035621462</v>
+        <v>-1.162419130736956</v>
       </c>
       <c r="G30">
-        <v>-3.43480860728927</v>
+        <v>-1.994557413921941</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>1.321029470563848</v>
       </c>
       <c r="E31">
-        <v>-26.45944751821089</v>
+        <v>-26.98866631806584</v>
       </c>
       <c r="F31">
-        <v>-1.053145873164062</v>
+        <v>-1.092478414183788</v>
       </c>
       <c r="G31">
-        <v>-3.068497644454756</v>
+        <v>-2.14670377645825</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>1.167350269143675</v>
       </c>
       <c r="E32">
-        <v>-26.1527660875629</v>
+        <v>-27.02049652965933</v>
       </c>
       <c r="F32">
-        <v>-1.145636407156238</v>
+        <v>-1.0851142279729</v>
       </c>
       <c r="G32">
-        <v>-2.740914466884816</v>
+        <v>-1.992813436535077</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>0.9743477634595646</v>
       </c>
       <c r="E33">
-        <v>-25.53176547064056</v>
+        <v>-26.3095871939771</v>
       </c>
       <c r="F33">
-        <v>-0.5256290855502949</v>
+        <v>-1.099554328538501</v>
       </c>
       <c r="G33">
-        <v>-2.367698084606808</v>
+        <v>-1.980294916220689</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>0.7666307007629752</v>
       </c>
       <c r="E34">
-        <v>-24.78667105254367</v>
+        <v>-25.54372671925607</v>
       </c>
       <c r="F34">
-        <v>-1.172607221423987</v>
+        <v>-1.110928641346342</v>
       </c>
       <c r="G34">
-        <v>-3.2281838373702</v>
+        <v>-2.527548754431492</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>0.5681123641105267</v>
       </c>
       <c r="E35">
-        <v>-25.725745358778</v>
+        <v>-25.37184191536671</v>
       </c>
       <c r="F35">
-        <v>-1.039906076965118</v>
+        <v>-1.009629248392796</v>
       </c>
       <c r="G35">
-        <v>-4.178288619712738</v>
+        <v>-2.610907218481148</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>0.3986852109193577</v>
       </c>
       <c r="E36">
-        <v>-24.12248534426577</v>
+        <v>-25.13873877654938</v>
       </c>
       <c r="F36">
-        <v>-0.7454761375184781</v>
+        <v>-1.139814641049363</v>
       </c>
       <c r="G36">
-        <v>-3.667822783535313</v>
+        <v>-2.696915588290784</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>0.2716476282527125</v>
       </c>
       <c r="E37">
-        <v>-24.24269173964028</v>
+        <v>-24.30029262750433</v>
       </c>
       <c r="F37">
-        <v>-0.8937978060919379</v>
+        <v>-0.8915761247176296</v>
       </c>
       <c r="G37">
-        <v>-3.062563421999155</v>
+        <v>-2.800797115571182</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>0.1924826211695549</v>
       </c>
       <c r="E38">
-        <v>-23.31854407490738</v>
+        <v>-23.78639087101534</v>
       </c>
       <c r="F38">
-        <v>-0.7823161210231805</v>
+        <v>-0.9493787737175764</v>
       </c>
       <c r="G38">
-        <v>-3.957362190923549</v>
+        <v>-2.501976511161537</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>0.1604828314978665</v>
       </c>
       <c r="E39">
-        <v>-22.50390828638756</v>
+        <v>-22.8105814106129</v>
       </c>
       <c r="F39">
-        <v>-0.9443414715411526</v>
+        <v>-1.061276299222539</v>
       </c>
       <c r="G39">
-        <v>-3.690491878819949</v>
+        <v>-2.772029320921704</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>0.1677445282752172</v>
       </c>
       <c r="E40">
-        <v>-22.20964911081213</v>
+        <v>-22.33419561202109</v>
       </c>
       <c r="F40">
-        <v>-1.229786109769626</v>
+        <v>-0.9352368854169831</v>
       </c>
       <c r="G40">
-        <v>-3.662026930543041</v>
+        <v>-2.934007747588146</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>0.2019670632778555</v>
       </c>
       <c r="E41">
-        <v>-21.87004517399223</v>
+        <v>-21.84890948156018</v>
       </c>
       <c r="F41">
-        <v>-0.1752180770224648</v>
+        <v>-0.6086853431919873</v>
       </c>
       <c r="G41">
-        <v>-3.420295478107271</v>
+        <v>-3.101881235541321</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>0.2488279868536809</v>
       </c>
       <c r="E42">
-        <v>-21.65934445706103</v>
+        <v>-21.50583346007272</v>
       </c>
       <c r="F42">
-        <v>-0.7214543112046952</v>
+        <v>-1.061610131285867</v>
       </c>
       <c r="G42">
-        <v>-4.425646226742357</v>
+        <v>-3.144201405363268</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>0.2906947856596631</v>
       </c>
       <c r="E43">
-        <v>-20.15108499839292</v>
+        <v>-20.87906818583151</v>
       </c>
       <c r="F43">
-        <v>-0.6432174951124903</v>
+        <v>-0.9070500278019245</v>
       </c>
       <c r="G43">
-        <v>-4.862713589485224</v>
+        <v>-3.250469153199943</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>0.3117282744178287</v>
       </c>
       <c r="E44">
-        <v>-19.73148190503417</v>
+        <v>-20.49773278161973</v>
       </c>
       <c r="F44">
-        <v>-0.7265313750164534</v>
+        <v>-1.006596595331147</v>
       </c>
       <c r="G44">
-        <v>-4.777692081131028</v>
+        <v>-3.180289727846227</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>0.2979510771120726</v>
       </c>
       <c r="E45">
-        <v>-19.56629207780044</v>
+        <v>-20.38466990972393</v>
       </c>
       <c r="F45">
-        <v>-0.5688458413217479</v>
+        <v>-0.7528063606658508</v>
       </c>
       <c r="G45">
-        <v>-3.862359805997528</v>
+        <v>-3.326063262835628</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>0.2364847558229471</v>
       </c>
       <c r="E46">
-        <v>-18.314244225761</v>
+        <v>-18.89129971365533</v>
       </c>
       <c r="F46">
-        <v>-0.6182563001639327</v>
+        <v>-0.712357180387151</v>
       </c>
       <c r="G46">
-        <v>-4.438172579290518</v>
+        <v>-3.420987325423916</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>0.120658708677422</v>
       </c>
       <c r="E47">
-        <v>-19.68656492455614</v>
+        <v>-17.96591439194763</v>
       </c>
       <c r="F47">
-        <v>-0.7395831318149624</v>
+        <v>-0.6385181668364087</v>
       </c>
       <c r="G47">
-        <v>-5.441233704919199</v>
+        <v>-3.596434583435911</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-0.05306588325666808</v>
       </c>
       <c r="E48">
-        <v>-17.05697163387493</v>
+        <v>-17.39751834966557</v>
       </c>
       <c r="F48">
-        <v>-0.7185276891706045</v>
+        <v>-0.8615444928965363</v>
       </c>
       <c r="G48">
-        <v>-4.182737328495995</v>
+        <v>-3.882144028508984</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-0.2851606212713529</v>
       </c>
       <c r="E49">
-        <v>-16.44975967855102</v>
+        <v>-17.84310808628377</v>
       </c>
       <c r="F49">
-        <v>-0.6964185631898857</v>
+        <v>-0.793845338535344</v>
       </c>
       <c r="G49">
-        <v>-4.623762580038989</v>
+        <v>-3.687152736487915</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-0.5697866403780124</v>
       </c>
       <c r="E50">
-        <v>-16.25023940650626</v>
+        <v>-16.54867671267446</v>
       </c>
       <c r="F50">
-        <v>-0.7768952847392605</v>
+        <v>-0.636285716685864</v>
       </c>
       <c r="G50">
-        <v>-4.830656256650943</v>
+        <v>-3.922153689367796</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-0.9029240102347902</v>
       </c>
       <c r="E51">
-        <v>-16.01558711986477</v>
+        <v>-15.94351644374502</v>
       </c>
       <c r="F51">
-        <v>-0.728210475741928</v>
+        <v>-0.7515505556832068</v>
       </c>
       <c r="G51">
-        <v>-5.483224920922665</v>
+        <v>-3.704349711109578</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-1.279454863168339</v>
       </c>
       <c r="E52">
-        <v>-16.03449253781539</v>
+        <v>-15.81474197340739</v>
       </c>
       <c r="F52">
-        <v>-0.973191023078451</v>
+        <v>-0.6883527497888269</v>
       </c>
       <c r="G52">
-        <v>-6.245682435778935</v>
+        <v>-3.943131022157391</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-1.691131250967925</v>
       </c>
       <c r="E53">
-        <v>-15.29239673829503</v>
+        <v>-14.084260789593</v>
       </c>
       <c r="F53">
-        <v>-0.7111187711199658</v>
+        <v>-0.86147159656509</v>
       </c>
       <c r="G53">
-        <v>-4.74805490853271</v>
+        <v>-4.422954549068919</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-2.137790585068183</v>
       </c>
       <c r="E54">
-        <v>-13.70098998890385</v>
+        <v>-14.54937477264922</v>
       </c>
       <c r="F54">
-        <v>-0.4238094778677908</v>
+        <v>-0.611785094013263</v>
       </c>
       <c r="G54">
-        <v>-5.670104629499145</v>
+        <v>-4.567454040697857</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-2.614766332277352</v>
       </c>
       <c r="E55">
-        <v>-13.92736492537495</v>
+        <v>-13.63298530667111</v>
       </c>
       <c r="F55">
-        <v>-0.02818617649516373</v>
+        <v>-0.5344917883928467</v>
       </c>
       <c r="G55">
-        <v>-6.030149805314987</v>
+        <v>-4.643646010844908</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-3.117570077808521</v>
       </c>
       <c r="E56">
-        <v>-11.93837540906927</v>
+        <v>-12.74334667483621</v>
       </c>
       <c r="F56">
-        <v>-0.2469074771629424</v>
+        <v>-0.5942485560959975</v>
       </c>
       <c r="G56">
-        <v>-5.809100671530016</v>
+        <v>-4.742997896259724</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-3.647564500989913</v>
       </c>
       <c r="E57">
-        <v>-13.0911282847547</v>
+        <v>-13.44909356884167</v>
       </c>
       <c r="F57">
-        <v>-0.4801865065675195</v>
+        <v>-0.713687538436047</v>
       </c>
       <c r="G57">
-        <v>-6.023455856183372</v>
+        <v>-5.351737380335836</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-4.199510525732475</v>
       </c>
       <c r="E58">
-        <v>-13.20633421369412</v>
+        <v>-12.56736680458057</v>
       </c>
       <c r="F58">
-        <v>-0.7917073222687184</v>
+        <v>-0.7716840254082488</v>
       </c>
       <c r="G58">
-        <v>-5.7090438850756</v>
+        <v>-5.63207913452958</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.7739035276233</v>
       </c>
       <c r="E59">
-        <v>-11.72135350450167</v>
+        <v>-11.57896896065258</v>
       </c>
       <c r="F59">
-        <v>-0.8821459902041601</v>
+        <v>-0.6063915938536354</v>
       </c>
       <c r="G59">
-        <v>-7.188223891041019</v>
+        <v>-5.69896118946472</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-5.372726005593567</v>
       </c>
       <c r="E60">
-        <v>-12.33002739021192</v>
+        <v>-12.13136267970007</v>
       </c>
       <c r="F60">
-        <v>-0.9016797219295752</v>
+        <v>-0.684828046489915</v>
       </c>
       <c r="G60">
-        <v>-6.912210751379339</v>
+        <v>-5.722664139607438</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-5.990370352781283</v>
       </c>
       <c r="E61">
-        <v>-11.92788439726275</v>
+        <v>-11.38433286512581</v>
       </c>
       <c r="F61">
-        <v>-0.4157105297706201</v>
+        <v>-0.9589522157917302</v>
       </c>
       <c r="G61">
-        <v>-7.247127510505716</v>
+        <v>-5.897954752943966</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-6.628413888294646</v>
       </c>
       <c r="E62">
-        <v>-10.91644038369328</v>
+        <v>-10.59580416299387</v>
       </c>
       <c r="F62">
-        <v>-0.8726388175222302</v>
+        <v>-0.6294591409193933</v>
       </c>
       <c r="G62">
-        <v>-6.638763973650725</v>
+        <v>-5.951383641001099</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-7.282254769757289</v>
       </c>
       <c r="E63">
-        <v>-10.61164035777544</v>
+        <v>-10.42186767271005</v>
       </c>
       <c r="F63">
-        <v>-0.8007133326719547</v>
+        <v>-0.6285313694282578</v>
       </c>
       <c r="G63">
-        <v>-6.093092246662137</v>
+        <v>-6.398888760619236</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-7.94003527113193</v>
       </c>
       <c r="E64">
-        <v>-10.11238697762912</v>
+        <v>-10.45032132349645</v>
       </c>
       <c r="F64">
-        <v>-1.163311282429771</v>
+        <v>-1.149049280855772</v>
       </c>
       <c r="G64">
-        <v>-7.035312580339514</v>
+        <v>-6.038357986309447</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-8.600039533250081</v>
       </c>
       <c r="E65">
-        <v>-9.80448865606296</v>
+        <v>-9.874885588018804</v>
       </c>
       <c r="F65">
-        <v>-1.010884225008037</v>
+        <v>-0.5868537202912063</v>
       </c>
       <c r="G65">
-        <v>-7.203133853400867</v>
+        <v>-6.826842013994527</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-9.25072561594083</v>
       </c>
       <c r="E66">
-        <v>-10.20912357580703</v>
+        <v>-9.252344129694954</v>
       </c>
       <c r="F66">
-        <v>-0.9652585768292429</v>
+        <v>-0.7156366869348343</v>
       </c>
       <c r="G66">
-        <v>-6.826332918799259</v>
+        <v>-6.73267245659307</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-9.88017543749554</v>
       </c>
       <c r="E67">
-        <v>-9.549385956858016</v>
+        <v>-9.473016707017068</v>
       </c>
       <c r="F67">
-        <v>-1.059792693204125</v>
+        <v>-0.8415211960360667</v>
       </c>
       <c r="G67">
-        <v>-6.950797556435994</v>
+        <v>-6.797497244790413</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-10.47936806460801</v>
       </c>
       <c r="E68">
-        <v>-9.937723675363459</v>
+        <v>-9.721607170864681</v>
       </c>
       <c r="F68">
-        <v>-0.8012211218898707</v>
+        <v>-1.213406801114071</v>
       </c>
       <c r="G68">
-        <v>-6.926778706197751</v>
+        <v>-6.870407508986434</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-11.03152629716534</v>
       </c>
       <c r="E69">
-        <v>-11.47414606002523</v>
+        <v>-8.876100562567412</v>
       </c>
       <c r="F69">
-        <v>-1.417188495672361</v>
+        <v>-1.148996265341993</v>
       </c>
       <c r="G69">
-        <v>-7.200739800610815</v>
+        <v>-6.175602218719681</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-11.52460612882878</v>
       </c>
       <c r="E70">
-        <v>-10.04110956487242</v>
+        <v>-9.009406186460433</v>
       </c>
       <c r="F70">
-        <v>-0.9283067637251625</v>
+        <v>-1.214043815646824</v>
       </c>
       <c r="G70">
-        <v>-7.33179395759552</v>
+        <v>-6.791782324880466</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-11.94854415415446</v>
       </c>
       <c r="E71">
-        <v>-9.87424599347478</v>
+        <v>-8.862415731252101</v>
       </c>
       <c r="F71">
-        <v>-1.338993097950296</v>
+        <v>-1.303644175770633</v>
       </c>
       <c r="G71">
-        <v>-7.9776765049694</v>
+        <v>-6.288328948674771</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-12.29154612906972</v>
       </c>
       <c r="E72">
-        <v>-9.30150569214695</v>
+        <v>-9.826251483405061</v>
       </c>
       <c r="F72">
-        <v>-1.333047905100404</v>
+        <v>-1.397928125189869</v>
       </c>
       <c r="G72">
-        <v>-6.892773757898501</v>
+        <v>-6.411062662647597</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-12.55167700196449</v>
       </c>
       <c r="E73">
-        <v>-8.583440373352044</v>
+        <v>-9.216784334331772</v>
       </c>
       <c r="F73">
-        <v>-1.377503898506445</v>
+        <v>-1.428510621333824</v>
       </c>
       <c r="G73">
-        <v>-6.32734913733355</v>
+        <v>-6.32376197426536</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-12.73013343635599</v>
       </c>
       <c r="E74">
-        <v>-9.858077541787223</v>
+        <v>-10.12728869986261</v>
       </c>
       <c r="F74">
-        <v>-1.64205876757112</v>
+        <v>-1.372307549788684</v>
       </c>
       <c r="G74">
-        <v>-6.088058731090471</v>
+        <v>-6.044357477379825</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-12.82709834997455</v>
       </c>
       <c r="E75">
-        <v>-10.04490560002331</v>
+        <v>-9.731703627595339</v>
       </c>
       <c r="F75">
-        <v>-1.488400756188826</v>
+        <v>-1.672469791662696</v>
       </c>
       <c r="G75">
-        <v>-5.882201520081188</v>
+        <v>-5.958262952998683</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-12.84838406408601</v>
       </c>
       <c r="E76">
-        <v>-11.1497262638089</v>
+        <v>-9.825732331989459</v>
       </c>
       <c r="F76">
-        <v>-1.574847521610177</v>
+        <v>-1.546746814205009</v>
       </c>
       <c r="G76">
-        <v>-5.516746881472559</v>
+        <v>-5.747056326322209</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-12.79882840804855</v>
       </c>
       <c r="E77">
-        <v>-11.21505212473713</v>
+        <v>-10.52848891384104</v>
       </c>
       <c r="F77">
-        <v>-1.579265204969306</v>
+        <v>-1.752381566643361</v>
       </c>
       <c r="G77">
-        <v>-6.390208034853785</v>
+        <v>-5.586451151310693</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-12.67982928226945</v>
       </c>
       <c r="E78">
-        <v>-11.02106808338836</v>
+        <v>-10.75821133863996</v>
       </c>
       <c r="F78">
-        <v>-1.941665174917854</v>
+        <v>-1.724836693765472</v>
       </c>
       <c r="G78">
-        <v>-5.871105855568957</v>
+        <v>-5.270759915353274</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-12.492059897897</v>
       </c>
       <c r="E79">
-        <v>-12.08098837954123</v>
+        <v>-10.9788382306375</v>
       </c>
       <c r="F79">
-        <v>-1.177431633177891</v>
+        <v>-1.464693709488107</v>
       </c>
       <c r="G79">
-        <v>-5.297875108676577</v>
+        <v>-5.210754561671127</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-12.23464536285139</v>
       </c>
       <c r="E80">
-        <v>-12.36551242777126</v>
+        <v>-12.1149907206576</v>
       </c>
       <c r="F80">
-        <v>-1.9224752156646</v>
+        <v>-1.608486693470462</v>
       </c>
       <c r="G80">
-        <v>-4.91917616275723</v>
+        <v>-4.947515795293765</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-11.90276223298004</v>
       </c>
       <c r="E81">
-        <v>-12.87330481040142</v>
+        <v>-12.60747851955577</v>
       </c>
       <c r="F81">
-        <v>-1.627980663560542</v>
+        <v>-1.574193939729368</v>
       </c>
       <c r="G81">
-        <v>-3.976308364421258</v>
+        <v>-4.617073852396556</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-11.49686971821792</v>
       </c>
       <c r="E82">
-        <v>-14.06367747426715</v>
+        <v>-12.50244795836218</v>
       </c>
       <c r="F82">
-        <v>-1.427738582914415</v>
+        <v>-1.514703077962516</v>
       </c>
       <c r="G82">
-        <v>-5.122947388838214</v>
+        <v>-4.33442942147345</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-11.01899603199365</v>
       </c>
       <c r="E83">
-        <v>-13.90075114720545</v>
+        <v>-13.86142854238198</v>
       </c>
       <c r="F83">
-        <v>-1.851682109053952</v>
+        <v>-1.850582865510437</v>
       </c>
       <c r="G83">
-        <v>-5.138820715952182</v>
+        <v>-4.243645999806668</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-10.46989204796362</v>
       </c>
       <c r="E84">
-        <v>-16.13705193827071</v>
+        <v>-14.76180737870288</v>
       </c>
       <c r="F84">
-        <v>-2.027556934179329</v>
+        <v>-1.780753978556647</v>
       </c>
       <c r="G84">
-        <v>-5.308435570547631</v>
+        <v>-4.163130636616734</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-9.863765590235696</v>
       </c>
       <c r="E85">
-        <v>-16.3037244619474</v>
+        <v>-15.12732735418972</v>
       </c>
       <c r="F85">
-        <v>-1.688190548233025</v>
+        <v>-1.773149565798948</v>
       </c>
       <c r="G85">
-        <v>-4.237354105342085</v>
+        <v>-4.143568327395522</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-9.212353274493465</v>
       </c>
       <c r="E86">
-        <v>-17.75925474963548</v>
+        <v>-16.9637777249571</v>
       </c>
       <c r="F86">
-        <v>-2.064734063216971</v>
+        <v>-1.995910814290179</v>
       </c>
       <c r="G86">
-        <v>-3.922448703506591</v>
+        <v>-3.764266299475628</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-8.528852787438012</v>
       </c>
       <c r="E87">
-        <v>-18.19259666605677</v>
+        <v>-17.99374921424663</v>
       </c>
       <c r="F87">
-        <v>-1.601973240582249</v>
+        <v>-1.904293379540554</v>
       </c>
       <c r="G87">
-        <v>-4.270304312826526</v>
+        <v>-3.199032263265829</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-7.834777045997268</v>
       </c>
       <c r="E88">
-        <v>-19.35210266335638</v>
+        <v>-19.35549999022009</v>
       </c>
       <c r="F88">
-        <v>-2.167763915674965</v>
+        <v>-2.19963369476287</v>
       </c>
       <c r="G88">
-        <v>-3.54591928634246</v>
+        <v>-3.651923348975433</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-7.145247327915984</v>
       </c>
       <c r="E89">
-        <v>-20.28635093803126</v>
+        <v>-20.37124257751075</v>
       </c>
       <c r="F89">
-        <v>-2.429899951923466</v>
+        <v>-2.094259562554953</v>
       </c>
       <c r="G89">
-        <v>-3.979428204207639</v>
+        <v>-2.987055466934977</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-6.477872522820047</v>
       </c>
       <c r="E90">
-        <v>-21.85129757807195</v>
+        <v>-22.46141262811192</v>
       </c>
       <c r="F90">
-        <v>-2.247428008802193</v>
+        <v>-2.197462543800133</v>
       </c>
       <c r="G90">
-        <v>-3.342119342070974</v>
+        <v>-3.117877267651072</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-5.85153043237402</v>
       </c>
       <c r="E91">
-        <v>-24.01079718531848</v>
+        <v>-23.37644399398681</v>
       </c>
       <c r="F91">
-        <v>-1.952943397106969</v>
+        <v>-2.251170572728042</v>
       </c>
       <c r="G91">
-        <v>-2.998803817594986</v>
+        <v>-3.049405269259944</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-5.276790442027518</v>
       </c>
       <c r="E92">
-        <v>-26.72863375701833</v>
+        <v>-24.71772774455152</v>
       </c>
       <c r="F92">
-        <v>-2.270950329572088</v>
+        <v>-2.446290029355257</v>
       </c>
       <c r="G92">
-        <v>-3.407957099169669</v>
+        <v>-3.274558493542145</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-4.771186201539928</v>
       </c>
       <c r="E93">
-        <v>-27.23473993585061</v>
+        <v>-26.93464134515247</v>
       </c>
       <c r="F93">
-        <v>-2.452029787089254</v>
+        <v>-2.492295069804533</v>
       </c>
       <c r="G93">
-        <v>-3.495685949664849</v>
+        <v>-3.146744270595012</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.347317473799058</v>
       </c>
       <c r="E94">
-        <v>-28.0930301286057</v>
+        <v>-28.9790222408974</v>
       </c>
       <c r="F94">
-        <v>-2.291923763843569</v>
+        <v>-2.715538428124194</v>
       </c>
       <c r="G94">
-        <v>-3.36103418663359</v>
+        <v>-2.749083486710409</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-4.011443470871966</v>
       </c>
       <c r="E95">
-        <v>-30.72719195174423</v>
+        <v>-30.54493657917677</v>
       </c>
       <c r="F95">
-        <v>-2.296880714381921</v>
+        <v>-2.813907057206635</v>
       </c>
       <c r="G95">
-        <v>-3.998173350371832</v>
+        <v>-2.659793410949744</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-3.771684543779691</v>
       </c>
       <c r="E96">
-        <v>-32.30980635276074</v>
+        <v>-32.30182595720008</v>
       </c>
       <c r="F96">
-        <v>-2.816197493075376</v>
+        <v>-2.906959224297909</v>
       </c>
       <c r="G96">
-        <v>-3.97326423622802</v>
+        <v>-3.018890886479012</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.623149092649111</v>
       </c>
       <c r="E97">
-        <v>-33.74943399428606</v>
+        <v>-35.04617455339198</v>
       </c>
       <c r="F97">
-        <v>-2.918456135481363</v>
+        <v>-3.006938199611393</v>
       </c>
       <c r="G97">
-        <v>-4.053962351539332</v>
+        <v>-2.955697813651115</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-3.554427307076267</v>
       </c>
       <c r="E98">
-        <v>-37.42033911777925</v>
+        <v>-36.44750335668539</v>
       </c>
       <c r="F98">
-        <v>-2.797421717523522</v>
+        <v>-3.205610524029215</v>
       </c>
       <c r="G98">
-        <v>-3.733543057127407</v>
+        <v>-3.05786147099056</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-3.549145348986452</v>
       </c>
       <c r="E99">
-        <v>-40.55111495526716</v>
+        <v>-38.87631795229041</v>
       </c>
       <c r="F99">
-        <v>-3.312559382669853</v>
+        <v>-3.066977440598898</v>
       </c>
       <c r="G99">
-        <v>-3.904807902304439</v>
+        <v>-3.290311726404922</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-3.584063358301894</v>
       </c>
       <c r="E100">
-        <v>-41.31947358660008</v>
+        <v>-41.27099315080535</v>
       </c>
       <c r="F100">
-        <v>-3.3948030118894</v>
+        <v>-3.420271996055873</v>
       </c>
       <c r="G100">
-        <v>-4.673157867702852</v>
+        <v>-3.263880548164492</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-3.634299018623271</v>
       </c>
       <c r="E101">
-        <v>-43.45980404697686</v>
+        <v>-42.57505997468827</v>
       </c>
       <c r="F101">
-        <v>-3.12975857768967</v>
+        <v>-3.482847698030751</v>
       </c>
       <c r="G101">
-        <v>-4.626830204933547</v>
+        <v>-3.818799532494803</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-3.678647541730745</v>
       </c>
       <c r="E102">
-        <v>-45.53352945733736</v>
+        <v>-45.02355663876166</v>
       </c>
       <c r="F102">
-        <v>-3.137594933320153</v>
+        <v>-3.59576494380856</v>
       </c>
       <c r="G102">
-        <v>-4.665701581150633</v>
+        <v>-3.523145761274179</v>
       </c>
     </row>
   </sheetData>
